--- a/test-execution/test-execution.xlsx
+++ b/test-execution/test-execution.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projets\Miniprojet-QA\test-execution\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projets\Campagne-QA\test-execution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D375C2F6-EC60-4F93-A9B6-6F9F20056705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C68B63-A085-4115-BBEF-F487D962E3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{68D144E3-1831-46A9-BC3E-14B45551544B}"/>
   </bookViews>
@@ -98,14 +98,6 @@
     <t>TC-006</t>
   </si>
   <si>
-    <t>Les quantités des différents produits sont passées de 1 à 2
-Le montant total à prit en compte les modifications</t>
-  </si>
-  <si>
-    <t>La quantité du produit est passée de 1 à 2
-Le montant total à prit en compte les modifications</t>
-  </si>
-  <si>
     <t>TC-007</t>
   </si>
   <si>
@@ -142,16 +134,6 @@
   <si>
     <t>Les produits sont toujours dans le panier
 Le bouton supprimer ne fonctionne pas</t>
-  </si>
-  <si>
-    <t>La quantité est passée de 1 à 2
-Le montant total à prit en compte les modifications
-Le total du produit reste figé à 0</t>
-  </si>
-  <si>
-    <t>La quantité des deux items est passée de 1 à 2
-Le montant total à prit en compte les modifications
-Le total de chaque produit reste figé à 0</t>
   </si>
   <si>
     <t>NOT TESTABLE</t>
@@ -203,6 +185,24 @@
   <si>
     <t>bug-report_006
 (nouveau bug report)</t>
+  </si>
+  <si>
+    <t>La quantité du produit est passée de 1 à 2
+Le montant total a pris en compte les modifications</t>
+  </si>
+  <si>
+    <t>La quantité est passée de 1 à 2
+Le montant total a pris en compte les modifications
+Le total du produit reste figé à 0</t>
+  </si>
+  <si>
+    <t>Les quantités des différents produits sont passées de 1 à 2
+Le montant total a pris en compte les modifications</t>
+  </si>
+  <si>
+    <t>La quantité des deux items est passée de 1 à 2
+Le montant total a pris en compte les modifications
+Le total de chaque produit reste figé à 0</t>
   </si>
 </sst>
 </file>
@@ -682,7 +682,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="52.5" x14ac:dyDescent="0.45">
@@ -693,13 +693,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="52.5" x14ac:dyDescent="0.45">
@@ -710,13 +710,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="52.5" x14ac:dyDescent="0.45">
@@ -727,13 +727,13 @@
         <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="78.75" x14ac:dyDescent="0.45">
@@ -741,16 +741,16 @@
         <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="78.75" x14ac:dyDescent="0.45">
@@ -758,75 +758,75 @@
         <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="52.5" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="52.5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" ht="52.5" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" ht="39.4" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E11" s="5"/>
     </row>
